--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CCBBDC-0591-4056-9324-3A47EB384D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18,26 +27,97 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>Название задачи</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Вес</t>
+  </si>
+  <si>
+    <t>Статус</t>
+  </si>
+  <si>
+    <t>Описание результата</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Создать GIT-репозиторий</t>
+  </si>
+  <si>
+    <t>Иницилизировать СУВ на базе GIT, связать с удаленным на сервере GitHub</t>
+  </si>
+  <si>
+    <t>Текущий</t>
+  </si>
+  <si>
+    <t>Создать бота в BotFather</t>
+  </si>
+  <si>
+    <t>Создать оболочку бота в Botfather</t>
+  </si>
+  <si>
+    <t>Настроить окружение</t>
+  </si>
+  <si>
+    <t>Установить необходимые библиотеки для работы с TelegramBOT api, настроить IDE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Trebuchet MS"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +125,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Акцент2" xfId="2" builtinId="33"/>
+    <cellStyle name="Вывод" xfId="1" builtinId="21"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -69,9 +176,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Аспект">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Аспект">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -79,52 +186,52 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="2C3C43"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EBEBEB"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="90C226"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="54A021"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="E6B91E"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="E76618"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="C42F1A"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="918655"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="99CA3C"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="B9D181"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Аспект">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Trebuchet MS" panose="020B0603020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="メイリオ"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Hans" typeface="方正姚体"/>
+        <a:font script="Hant" typeface="微軟正黑體"/>
+        <a:font script="Arab" typeface="Tahoma"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
         <a:font script="Knda" typeface="Tunga"/>
         <a:font script="Guru" typeface="Raavi"/>
         <a:font script="Cans" typeface="Euphemia"/>
@@ -141,21 +248,21 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Viet" typeface="Tahoma"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Trebuchet MS" panose="020B0603020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Jpan" typeface="メイリオ"/>
+        <a:font script="Hang" typeface="HY그래픽M"/>
+        <a:font script="Hans" typeface="华文新魏"/>
+        <a:font script="Hant" typeface="微軟正黑體"/>
+        <a:font script="Arab" typeface="Tahoma"/>
+        <a:font script="Hebr" typeface="Gisha"/>
+        <a:font script="Thai" typeface="IrisUPC"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -181,7 +288,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Аспект">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -190,23 +297,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="65000"/>
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="88000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="90000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -216,23 +313,14 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="96000"/>
+                <a:lumMod val="100000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="78000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:lumMod val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -240,26 +328,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="rnd" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="rnd" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -267,54 +352,72 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="38100" dist="25400" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="50800" dist="38100" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="tl"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="plastic">
+            <a:bevelT w="0" h="0"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="90000"/>
+                <a:lumMod val="104000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="94000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:shade val="96000"/>
+                <a:lumMod val="82000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="90000"/>
+                <a:lumMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="94000"/>
+                <a:lumMod val="96000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="100000" b="100000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -323,17 +426,317 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Facet" id="{C0C680CD-088A-49FC-A102-D699147F32B2}" vid="{CFBC31BA-B70F-4F30-BCAA-4F3011E16C4D}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CCBBDC-0591-4056-9324-3A47EB384D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3D3194-518E-4752-B495-7909D729B7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Название задачи</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Установить необходимые библиотеки для работы с TelegramBOT api, настроить IDE</t>
+  </si>
+  <si>
+    <t>Готово к тестированию</t>
+  </si>
+  <si>
+    <t>Создан гит репозиторий, и связан с удаленным сервером: https://github.com/Dimakodim/kursovaia-1</t>
   </si>
 </sst>
 </file>
@@ -441,8 +447,8 @@
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="25.5546875" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -479,9 +485,11 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3D3194-518E-4752-B495-7909D729B7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ED04FA-89E0-4AFB-A32B-5DD3D18BDEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Название задачи</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Создан гит репозиторий, и связан с удаленным сервером: https://github.com/Dimakodim/kursovaia-1</t>
+  </si>
+  <si>
+    <t>Создан и настроен бот в BotFarher: @QueueIKITBot</t>
   </si>
 </sst>
 </file>
@@ -507,7 +510,9 @@
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ED04FA-89E0-4AFB-A32B-5DD3D18BDEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138E6053-3783-4B7D-85F3-174522BDDBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Название задачи</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Иницилизировать СУВ на базе GIT, связать с удаленным на сервере GitHub</t>
   </si>
   <si>
-    <t>Текущий</t>
-  </si>
-  <si>
     <t>Создать бота в BotFather</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>Создан и настроен бот в BotFarher: @QueueIKITBot</t>
+  </si>
+  <si>
+    <t>Установлены необходимые библиотеки, написан простейщий бот, создано виртуальное окружение</t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
   <cols>
     <col min="1" max="1" width="6.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="33.21875" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" customWidth="1"/>
     <col min="6" max="6" width="42.33203125" customWidth="1"/>
@@ -488,10 +488,10 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -499,19 +499,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -519,18 +519,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="4">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138E6053-3783-4B7D-85F3-174522BDDBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15087B0-DDE7-49BC-9859-2ADBF53C5392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Название задачи</t>
   </si>
@@ -76,6 +87,9 @@
   </si>
   <si>
     <t>Установлены необходимые библиотеки, написан простейщий бот, создано виртуальное окружение</t>
+  </si>
+  <si>
+    <t>СПРИНТ 1</t>
   </si>
 </sst>
 </file>
@@ -126,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,13 +163,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
@@ -164,6 +187,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -443,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" customWidth="1"/>
@@ -454,7 +480,7 @@
     <col min="6" max="6" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -474,7 +500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -493,8 +519,11 @@
       <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -513,8 +542,9 @@
       <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -533,8 +563,9 @@
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -542,7 +573,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -550,7 +581,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -558,7 +589,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -566,7 +597,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -574,7 +605,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -582,7 +613,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -590,7 +621,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -598,7 +629,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -606,7 +637,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -614,7 +645,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -622,7 +653,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -752,6 +783,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="G2:G4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15087B0-DDE7-49BC-9859-2ADBF53C5392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9953387-A10D-4AB6-AEFD-E4BC282B28CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Название задачи</t>
   </si>
@@ -90,6 +90,30 @@
   </si>
   <si>
     <t>СПРИНТ 1</t>
+  </si>
+  <si>
+    <t>Создать БД</t>
+  </si>
+  <si>
+    <t>Текущий</t>
+  </si>
+  <si>
+    <t>Подключить БД к боту</t>
+  </si>
+  <si>
+    <t>Установить sqlite3 для Python и подключить созданную БД</t>
+  </si>
+  <si>
+    <t>Реализовать простейшее взаимодействие с БД через бота</t>
+  </si>
+  <si>
+    <t>Установить SQLiteStudio и создать каркас БД (Таблица пользователей, Таблица очередей)</t>
+  </si>
+  <si>
+    <t>Реализоват функционал для следующих комманд: 1) /start - поприветствовать пользователя и сохранить его ID в БД; 2) /create - создать очередь и сохоанить ее в БД; 3) /list - вывести лист всех очередей, созданных пользователем</t>
+  </si>
+  <si>
+    <t>СПРИНТ 2</t>
   </si>
 </sst>
 </file>
@@ -565,29 +589,64 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+    <row r="5" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="G5" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
@@ -783,8 +842,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="G2:G4"/>
+    <mergeCell ref="G5:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9953387-A10D-4AB6-AEFD-E4BC282B28CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6BF8AD-5406-4162-8091-A4BE39AC84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Название задачи</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>СПРИНТ 2</t>
+  </si>
+  <si>
+    <t>Создана база данных data.db, созданы таблицы с пользователями и с очередями</t>
   </si>
 </sst>
 </file>
@@ -603,9 +606,11 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="G5" s="5" t="s">
         <v>24</v>
       </c>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6BF8AD-5406-4162-8091-A4BE39AC84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D39A3A-07DE-4792-8B71-9C47DD875546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>Название задачи</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Создать БД</t>
   </si>
   <si>
-    <t>Текущий</t>
-  </si>
-  <si>
     <t>Подключить БД к боту</t>
   </si>
   <si>
@@ -117,6 +114,12 @@
   </si>
   <si>
     <t>Создана база данных data.db, созданы таблицы с пользователями и с очередями</t>
+  </si>
+  <si>
+    <t>Установлена библиотека sqlite3, БД подключена к боту</t>
+  </si>
+  <si>
+    <t>Реализованы тербуемые комманды</t>
   </si>
 </sst>
 </file>
@@ -600,7 +603,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4">
         <v>2</v>
@@ -609,10 +612,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -620,18 +623,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="D6" s="4">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -639,18 +644,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4">
         <v>10</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D39A3A-07DE-4792-8B71-9C47DD875546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6864BA-20E4-4A4D-ABC4-337C48DE947B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Название задачи</t>
   </si>
@@ -120,13 +120,40 @@
   </si>
   <si>
     <t>Реализованы тербуемые комманды</t>
+  </si>
+  <si>
+    <t>СПРИНТ 3</t>
+  </si>
+  <si>
+    <t>Построить архитектуру БД</t>
+  </si>
+  <si>
+    <t>Построить архитектуру БД, пригодную для работы бота</t>
+  </si>
+  <si>
+    <t>Текущий</t>
+  </si>
+  <si>
+    <t>Построить архитектуру кода</t>
+  </si>
+  <si>
+    <t>Построить архитектуру кода приложения, оптимальную для разработки</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Создать модуль "Главное меню"</t>
+  </si>
+  <si>
+    <t>Создать модуль главное меню: 
+1) Переход в модуль - команда /start
+2) Сообщение бота: приветствование пользователя, описание функционала и доступные комманды
+3) Клавиатура: Мои очереди, Создать очередь, Присоедениться к очереди</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +176,12 @@
       <name val="Trebuchet MS"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -208,7 +241,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
@@ -220,6 +253,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -660,29 +696,64 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+    <row r="8" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="G8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -854,10 +925,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G8:G10"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6864BA-20E4-4A4D-ABC4-337C48DE947B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321FEB7C-E183-45EF-B84D-3B07D6A4A6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>Название задачи</t>
   </si>
@@ -147,6 +147,9 @@
 1) Переход в модуль - команда /start
 2) Сообщение бота: приветствование пользователя, описание функционала и доступные комманды
 3) Клавиатура: Мои очереди, Создать очередь, Присоедениться к очереди</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расширен архитектура БД, добавлены строки с кодом подключения, списком участников и настройки очереди </t>
   </si>
 </sst>
 </file>
@@ -710,9 +713,11 @@
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="G8" s="5" t="s">
         <v>27</v>
       </c>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321FEB7C-E183-45EF-B84D-3B07D6A4A6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D726C76A-DC05-47BC-93A1-87705A615BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Название задачи</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t xml:space="preserve">Расширен архитектура БД, добавлены строки с кодом подключения, списком участников и настройки очереди </t>
+  </si>
+  <si>
+    <t>Построена архитектура кода, добавлен инструмент разработчика для создания модуля, добавлен README.md с описанием структуры папок и командами для разработчика</t>
   </si>
 </sst>
 </file>
@@ -736,9 +739,11 @@
         <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D726C76A-DC05-47BC-93A1-87705A615BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9F8442-46C4-4E92-964B-7EBB68D0E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Название задачи</t>
   </si>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>Построить архитектуру БД, пригодную для работы бота</t>
-  </si>
-  <si>
-    <t>Текущий</t>
   </si>
   <si>
     <t>Построить архитектуру кода</t>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>Построена архитектура кода, добавлен инструмент разработчика для создания модуля, добавлен README.md с описанием структуры папок и командами для разработчика</t>
+  </si>
+  <si>
+    <t>С помощью созданной команды был сделан соответсвующий модуль, в него была добавлена необходимая логика, создана клавиатура</t>
   </si>
 </sst>
 </file>
@@ -257,11 +257,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -591,7 +591,7 @@
       <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -614,7 +614,7 @@
       <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
@@ -635,7 +635,7 @@
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
@@ -656,7 +656,7 @@
       <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
@@ -700,7 +700,7 @@
       <c r="F7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
@@ -719,9 +719,9 @@
         <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -730,10 +730,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D9" s="4">
         <v>10</v>
@@ -742,28 +742,30 @@
         <v>12</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="D10" s="4">
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9F8442-46C4-4E92-964B-7EBB68D0E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FBB88F-8446-4962-9722-83058C89DB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Название задачи</t>
   </si>
@@ -153,6 +153,32 @@
   </si>
   <si>
     <t>С помощью созданной команды был сделан соответсвующий модуль, в него была добавлена необходимая логика, создана клавиатура</t>
+  </si>
+  <si>
+    <t>Расширить функционал инструментов разработчика</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди"</t>
+  </si>
+  <si>
+    <t>Создать модуль "Присоединение к очереди"</t>
+  </si>
+  <si>
+    <t>Текущий</t>
+  </si>
+  <si>
+    <t>Добавить автогенерацию контента к инструменту создания модулей. 
+Придумать новые инструменты.</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди":
+1) Переход в модуль - через модуль главное меню, или команду /create
+2) Логика работы: запросить название очереди -&gt; создать очередь в бд -&gt; сгенерировать и показать код доступа</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди":
+1) Переход в модуль - через модуль главное меню, или команду /join
+2) Логика работы: запросить код доступа -&gt; найти очередь в бд -&gt; добавить пользователя в конец очереди</t>
   </si>
 </sst>
 </file>
@@ -767,29 +793,59 @@
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+    <row r="11" spans="1:7" ht="106.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="4">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="184.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FBB88F-8446-4962-9722-83058C89DB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7E83F5-7909-4EDF-B6C2-E14C88C1108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>Название задачи</t>
   </si>
@@ -179,6 +179,9 @@
     <t>Создать модуль "Создание очереди":
 1) Переход в модуль - через модуль главное меню, или команду /join
 2) Логика работы: запросить код доступа -&gt; найти очередь в бд -&gt; добавить пользователя в конец очереди</t>
+  </si>
+  <si>
+    <t>Взято в работу</t>
   </si>
 </sst>
 </file>
@@ -807,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" s="4"/>
     </row>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7E83F5-7909-4EDF-B6C2-E14C88C1108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292AFCEE-3BE5-4271-8B28-C8289C318670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,7 +828,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F12" s="4"/>
     </row>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292AFCEE-3BE5-4271-8B28-C8289C318670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B7547-75AF-4900-AD59-EE11391B6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>Название задачи</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Создать модуль "Присоединение к очереди"</t>
   </si>
   <si>
-    <t>Текущий</t>
-  </si>
-  <si>
     <t>Добавить автогенерацию контента к инструменту создания модулей. 
 Придумать новые инструменты.</t>
   </si>
@@ -181,7 +178,13 @@
 2) Логика работы: запросить код доступа -&gt; найти очередь в бд -&gt; добавить пользователя в конец очереди</t>
   </si>
   <si>
-    <t>Взято в работу</t>
+    <t>Добавлена автогенерация контента к инструменту создания очередей</t>
+  </si>
+  <si>
+    <t>Создан соответсвующий модуль</t>
+  </si>
+  <si>
+    <t>СПРИНТ 4</t>
   </si>
 </sst>
 </file>
@@ -804,15 +807,20 @@
         <v>37</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
@@ -822,7 +830,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4">
         <v>7</v>
@@ -830,7 +838,10 @@
       <c r="E12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="184.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
@@ -840,15 +851,18 @@
         <v>39</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="4">
         <v>5</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
@@ -996,10 +1010,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G10"/>
+    <mergeCell ref="G11:G13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B7547-75AF-4900-AD59-EE11391B6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7A7763-FEEF-49C7-BD45-54A404D0184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9F8442-46C4-4E92-964B-7EBB68D0E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7A7763-FEEF-49C7-BD45-54A404D0184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>Название задачи</t>
   </si>
@@ -153,6 +153,38 @@
   </si>
   <si>
     <t>С помощью созданной команды был сделан соответсвующий модуль, в него была добавлена необходимая логика, создана клавиатура</t>
+  </si>
+  <si>
+    <t>Расширить функционал инструментов разработчика</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди"</t>
+  </si>
+  <si>
+    <t>Создать модуль "Присоединение к очереди"</t>
+  </si>
+  <si>
+    <t>Добавить автогенерацию контента к инструменту создания модулей. 
+Придумать новые инструменты.</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди":
+1) Переход в модуль - через модуль главное меню, или команду /create
+2) Логика работы: запросить название очереди -&gt; создать очередь в бд -&gt; сгенерировать и показать код доступа</t>
+  </si>
+  <si>
+    <t>Создать модуль "Создание очереди":
+1) Переход в модуль - через модуль главное меню, или команду /join
+2) Логика работы: запросить код доступа -&gt; найти очередь в бд -&gt; добавить пользователя в конец очереди</t>
+  </si>
+  <si>
+    <t>Добавлена автогенерация контента к инструменту создания очередей</t>
+  </si>
+  <si>
+    <t>Создан соответсвующий модуль</t>
+  </si>
+  <si>
+    <t>СПРИНТ 4</t>
   </si>
 </sst>
 </file>
@@ -767,29 +799,70 @@
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+    <row r="11" spans="1:7" ht="106.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="4">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="184.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="4">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
@@ -937,10 +1010,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G10"/>
+    <mergeCell ref="G11:G13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7A7763-FEEF-49C7-BD45-54A404D0184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CDA83B-AB8F-4C96-A9FC-E75F9765D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>Название задачи</t>
   </si>
@@ -185,6 +185,35 @@
   </si>
   <si>
     <t>СПРИНТ 4</t>
+  </si>
+  <si>
+    <t>Добавить Docker к проекту</t>
+  </si>
+  <si>
+    <t>Создать DockerFile, подключить к нему образ Python и необходимые библиотеки</t>
+  </si>
+  <si>
+    <t>Создан DockerFile, контейнер собирается и запускается</t>
+  </si>
+  <si>
+    <t>Создать модуль "Мои очереди"</t>
+  </si>
+  <si>
+    <t>Создать модуль "Мои очереди":
+1) Переход в модуль - через модуль главное меню, или команду /list
+2) Логика работы: найти в бд очереди, в которых есть пользователь -&gt; отобразить пользователю</t>
+  </si>
+  <si>
+    <t>Запустить бота на сервере</t>
+  </si>
+  <si>
+    <t>Залить код на сервер и запустить его</t>
+  </si>
+  <si>
+    <t>Код успешно запустился на сервере и работает</t>
+  </si>
+  <si>
+    <t>СПРИНТ 5</t>
   </si>
 </sst>
 </file>
@@ -864,29 +893,70 @@
       </c>
       <c r="G13" s="6"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+    <row r="14" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
@@ -1010,11 +1080,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G10"/>
     <mergeCell ref="G11:G13"/>
+    <mergeCell ref="G14:G16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CDA83B-AB8F-4C96-A9FC-E75F9765D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37459CC-CDF3-4889-BA64-E41B350ACF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>Название задачи</t>
   </si>
@@ -214,6 +214,35 @@
   </si>
   <si>
     <t>СПРИНТ 5</t>
+  </si>
+  <si>
+    <t>Создать модуль
+"Просмотр очереди"</t>
+  </si>
+  <si>
+    <t>Создать модуль "Просмотр очереди":
+1) Переход в модуль - нажатие кнопки с соответсвующим индексом очереди из клавиатуры модуля "Мои Очереди"</t>
+  </si>
+  <si>
+    <t>Текущий</t>
+  </si>
+  <si>
+    <t>СПРИНТ 6</t>
+  </si>
+  <si>
+    <t>Исправить орфаграфические ошибки в модулях бота</t>
+  </si>
+  <si>
+    <t>Исправить орфаграфические ошибки, согласно нормам русского языка</t>
+  </si>
+  <si>
+    <t>Взято в работу</t>
+  </si>
+  <si>
+    <t>Добавить функционал смены позиции в очереди</t>
+  </si>
+  <si>
+    <t>Добавить кнопки "Я сдал", "Пропустить одного человека", "В конец очереди", "Покинуть очередь"</t>
   </si>
 </sst>
 </file>
@@ -958,31 +987,60 @@
       </c>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -990,7 +1048,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -998,7 +1056,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1006,7 +1064,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1014,7 +1072,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1022,7 +1080,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1030,7 +1088,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1038,7 +1096,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1046,7 +1104,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1054,7 +1112,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1062,7 +1120,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1070,7 +1128,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1080,7 +1138,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="G17:G19"/>
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G8:G10"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37459CC-CDF3-4889-BA64-E41B350ACF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AEC210-588C-497C-BB59-EBFA200DCEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>Название задачи</t>
   </si>
@@ -236,13 +236,10 @@
     <t>Исправить орфаграфические ошибки, согласно нормам русского языка</t>
   </si>
   <si>
-    <t>Взято в работу</t>
-  </si>
-  <si>
-    <t>Добавить функционал смены позиции в очереди</t>
-  </si>
-  <si>
     <t>Добавить кнопки "Я сдал", "Пропустить одного человека", "В конец очереди", "Покинуть очередь"</t>
+  </si>
+  <si>
+    <t>Добавить инлайн клавиатуру для смены позиции в очереди</t>
   </si>
 </sst>
 </file>
@@ -997,9 +994,11 @@
       <c r="C17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>10</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="6" t="s">
@@ -1016,7 +1015,9 @@
       <c r="C18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
       <c r="E18" s="4" t="s">
         <v>57</v>
       </c>
@@ -1031,11 +1032,13 @@
         <v>62</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
       <c r="E19" s="4" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="6"/>

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AEC210-588C-497C-BB59-EBFA200DCEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77631693-CA91-4A27-B56C-D8F8202F383F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>Название задачи</t>
   </si>
@@ -224,9 +224,6 @@
 1) Переход в модуль - нажатие кнопки с соответсвующим индексом очереди из клавиатуры модуля "Мои Очереди"</t>
   </si>
   <si>
-    <t>Текущий</t>
-  </si>
-  <si>
     <t>СПРИНТ 6</t>
   </si>
   <si>
@@ -240,6 +237,15 @@
   </si>
   <si>
     <t>Добавить инлайн клавиатуру для смены позиции в очереди</t>
+  </si>
+  <si>
+    <t>Создан соответсвуюй модуль</t>
+  </si>
+  <si>
+    <t>Ошибки исправлены</t>
+  </si>
+  <si>
+    <t>Кнопки созданы и приклепены к необходимым сообщениям</t>
   </si>
 </sst>
 </file>
@@ -1000,9 +1006,11 @@
       <c r="E17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="G17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1010,18 +1018,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="D18" s="4">
         <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1029,10 +1039,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
@@ -1040,7 +1050,9 @@
       <c r="E19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">

--- a/Бэклог.xlsx
+++ b/Бэклог.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IKIT\КУРСОВАЯ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77631693-CA91-4A27-B56C-D8F8202F383F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886258E8-3EC7-4E07-B66E-B2EE2F14BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>Название задачи</t>
   </si>
@@ -246,6 +246,27 @@
   </si>
   <si>
     <t>Кнопки созданы и приклепены к необходимым сообщениям</t>
+  </si>
+  <si>
+    <t>Добавить функционал изменения очереди</t>
+  </si>
+  <si>
+    <t>Добавить функционал администрирования очереди</t>
+  </si>
+  <si>
+    <t>Финальное тестирование системы и исправление ошибок</t>
+  </si>
+  <si>
+    <t>Добавить функционал кнопкам "Я сдал", "Пропустить одного человека", "В конец очереди", "Покинуть очередь"</t>
+  </si>
+  <si>
+    <t>Добавить функционал для администрирования очереди: клавиатура администратора, удаление очереди, человека из очереди</t>
+  </si>
+  <si>
+    <t>Провести тестирование системы, исправить найденные ошибки</t>
+  </si>
+  <si>
+    <t>Текущий</t>
   </si>
 </sst>
 </file>
@@ -340,13 +361,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -666,417 +684,447 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>10</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>10</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="106.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>7</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="184.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>5</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>8</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>7</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>5</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>10</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>3</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="3">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+    <row r="21" spans="1:7" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+    <row r="22" spans="1:7" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="3">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
